--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2385-1022-CM25</t>
+          <t>3858-315-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15201.54</v>
+        <v>33893.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2429-2875-CM25</t>
+          <t>1233623-310-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24981.79</v>
+        <v>6267.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>558869-293-CM25</t>
+          <t>1233623-499-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>60037.05</v>
+        <v>7139.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2385-1103-CM25</t>
+          <t>2385-1022-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10176.74</v>
+        <v>15201.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1233623-1319-CM25</t>
+          <t>2429-2875-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6294.15</v>
+        <v>24981.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2385-1120-CM25</t>
+          <t>558869-293-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1657.43</v>
+        <v>60037.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1233623-1520-CM25</t>
+          <t>2385-1103-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>434.83</v>
+        <v>10176.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1233623-1519-CM25</t>
+          <t>1233623-1319-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>49245.13</v>
+        <v>6294.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233623-1517-CM25</t>
+          <t>2385-1120-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6961.5</v>
+        <v>1657.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233623-1516-CM25</t>
+          <t>1233623-1520-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7854</v>
+        <v>434.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1233623-1515-CM25</t>
+          <t>1233623-1517-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>73468.42</v>
+        <v>6961.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233623-1394-CM25</t>
+          <t>1233623-1516-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1176.91</v>
+        <v>7854</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1261592-8545-CM25</t>
+          <t>1233623-1515-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>70477.87</v>
+        <v>73468.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2429-3146-CM25</t>
+          <t>1233623-1394-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>32349.2</v>
+        <v>1176.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4291-3056-CM25</t>
+          <t>1233623-1519-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5660.38</v>
+        <v>49245.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3858-18-CM26</t>
+          <t>1261592-8545-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2087.24</v>
+        <v>70477.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2385-40-CM26</t>
+          <t>2429-3146-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4914.64</v>
+        <v>32349.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922070-9-CM26</t>
+          <t>4291-3056-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1701</v>
+        <v>5660.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2385-81-CM26</t>
+          <t>3858-18-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1944.91</v>
+        <v>2087.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2429-167-CM26</t>
+          <t>2385-40-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3094.83</v>
+        <v>4914.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>707415-28-CM26</t>
+          <t>922070-9-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Zona de Bienestar Antofagasta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>259.42</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2429-228-CM26</t>
+          <t>2385-81-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2057.27</v>
+        <v>1944.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3858-106-CM26</t>
+          <t>2429-167-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5357.86</v>
+        <v>3094.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3858-108-CM26</t>
+          <t>707415-28-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.095.533-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2717.96</v>
+        <v>259.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2385-172-CM26</t>
+          <t>2429-228-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>955.5700000000001</v>
+        <v>2057.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4291-223-CM26</t>
+          <t>3858-106-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2292</v>
+        <v>5357.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2258-2320-CM26</t>
+          <t>3858-108-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>15987.89</v>
+        <v>2717.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1113265-24-CM26</t>
+          <t>2385-172-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>52549.81</v>
+        <v>955.5700000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1113265-26-CM26</t>
+          <t>4291-223-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>17905.34</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>558869-51-CM26</t>
+          <t>2258-2320-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8473.32</v>
+        <v>15987.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2429-348-CM26</t>
+          <t>1113265-24-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>36042.24</v>
+        <v>52549.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1233623-123-CM26</t>
+          <t>1113265-26-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2777.46</v>
+        <v>17905.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2605-22-CM26</t>
+          <t>558869-51-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2678.68</v>
+        <v>8473.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1233623-159-CM26</t>
+          <t>2429-348-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8206.24</v>
+        <v>36042.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1261592-372-CM26</t>
+          <t>1233623-123-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>30769.12</v>
+        <v>2777.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3858-205-CM26</t>
+          <t>2605-22-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>671.16</v>
+        <v>2678.68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3858-208-CM26</t>
+          <t>1233623-159-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>11375.86</v>
+        <v>8206.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2385-272-CM26</t>
+          <t>1261592-372-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,22 +2786,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>17133.29</v>
+        <v>30769.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2605-30-CM26</t>
+          <t>3858-205-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>746.2</v>
+        <v>671.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2385-317-CM26</t>
+          <t>2385-272-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>6939.65</v>
+        <v>17133.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3053-12-CM26</t>
+          <t>3858-208-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>25919.39</v>
+        <v>11375.86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2429-573-CM26</t>
+          <t>2605-30-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>30023.35</v>
+        <v>746.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4291-624-CM26</t>
+          <t>2385-317-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1517.25</v>
+        <v>6939.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3917-113-CM26</t>
+          <t>3053-12-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10055.74</v>
+        <v>25919.39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3917-115-CM26</t>
+          <t>2429-573-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7150.39</v>
+        <v>30023.35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1220203-67-CM26</t>
+          <t>4291-624-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>21793.56</v>
+        <v>1517.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1233822-41-CM26</t>
+          <t>3917-113-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>17725.86</v>
+        <v>10055.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4291-699-CM26</t>
+          <t>3917-115-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12026.22</v>
+        <v>7150.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1233822-39-CM26</t>
+          <t>1220203-67-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26022.92</v>
+        <v>21793.56</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3053-19-CM26</t>
+          <t>4291-699-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6814.49</v>
+        <v>12026.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1230848-128-CM26</t>
+          <t>1233822-41-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12732.27</v>
+        <v>17725.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1220203-68-CM26</t>
+          <t>1233822-39-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3816.45</v>
+        <v>26022.92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4291-742-CM26</t>
+          <t>3053-19-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>904.4</v>
+        <v>6814.49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4291-756-CM26</t>
+          <t>1230848-128-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2345.42</v>
+        <v>12732.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2385-469-CM26</t>
+          <t>1220203-68-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2885.27</v>
+        <v>3816.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4291-856-CM26</t>
+          <t>4291-742-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>15346.24</v>
+        <v>904.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1261592-723-CM26</t>
+          <t>4291-756-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3811.76</v>
+        <v>2345.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1261592-724-CM26</t>
+          <t>2385-469-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>11435.28</v>
+        <v>2885.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1261592-722-CM26</t>
+          <t>4291-856-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,22 +4067,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>15247.04</v>
+        <v>15346.24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1261592-720-CM26</t>
+          <t>1261592-723-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8894.110000000001</v>
+        <v>3811.76</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1261592-673-CM26</t>
+          <t>1261592-724-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>16292.53</v>
+        <v>11435.28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2605-55-CM26</t>
+          <t>1261592-722-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2240.94</v>
+        <v>15247.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1261592-721-CM26</t>
+          <t>1261592-673-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>12705.87</v>
+        <v>16292.53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1230848-135-CM26</t>
+          <t>1261592-720-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,27 +4367,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2712.01</v>
+        <v>8894.110000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1261592-769-CM26</t>
+          <t>2605-55-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2541.17</v>
+        <v>2240.94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2384-118-CM26</t>
+          <t>1261592-721-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,27 +4489,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>23243.56</v>
+        <v>12705.87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2384-119-CM26</t>
+          <t>1230848-135-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4871.55</v>
+        <v>2712.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2384-120-CM26</t>
+          <t>1261592-769-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3101.41</v>
+        <v>2541.17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>664-36-CM26</t>
+          <t>2384-118-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2784.36</v>
+        <v>23243.56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3845-42-CM26</t>
+          <t>2384-119-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>27096.3</v>
+        <v>4871.55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1498185-191-CM26</t>
+          <t>2384-120-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>65.483.190-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FUND CENTRO CULTURAL PALACIO DE LA MONEDA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4517.24</v>
+        <v>3101.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922070-185-CM26</t>
+          <t>664-36-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3393.88</v>
+        <v>2784.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922070-186-CM26</t>
+          <t>3845-42-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>848.47</v>
+        <v>27096.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2385-528-CM26</t>
+          <t>1498185-191-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>65.483.190-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>FUND CENTRO CULTURAL PALACIO DE LA MONEDA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7640.64</v>
+        <v>4517.24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1158-99-CM26</t>
+          <t>922070-185-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Zona de Bienestar Antofagasta</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2547.98</v>
+        <v>3393.88</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3858-332-CM26</t>
+          <t>2385-528-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1432.83</v>
+        <v>7640.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3834-243-CM26</t>
+          <t>922070-186-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Zona de Bienestar Antofagasta</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1057.51</v>
+        <v>848.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1261592-925-CM26</t>
+          <t>1158-99-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,6 +5266,189 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
+        <v>2547.98</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3858-332-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>1432.83</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3834-243-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1057.51</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1261592-925-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
         <v>22355.1</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3858-315-CM25</t>
+          <t>4291-24-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>33893.4</v>
+        <v>44125.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1233623-310-CM25</t>
+          <t>4291-83-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6267.02</v>
+        <v>10347.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1233623-499-CM25</t>
+          <t>3149-78-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7139.86</v>
+        <v>26700.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2385-1022-CM25</t>
+          <t>3834-48-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15201.54</v>
+        <v>5625.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2429-2875-CM25</t>
+          <t>3858-61-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24981.79</v>
+        <v>8522.780000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>558869-293-CM25</t>
+          <t>4051-74-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>60037.05</v>
+        <v>8094.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2385-1103-CM25</t>
+          <t>1375735-11-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10176.74</v>
+        <v>45410.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1233623-1319-CM25</t>
+          <t>4468-72-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6294.15</v>
+        <v>2941.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2385-1120-CM25</t>
+          <t>4468-73-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,28 +1057,28 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1657.43</v>
+        <v>2941.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233623-1520-CM25</t>
+          <t>2429-1808-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>434.83</v>
+        <v>44561.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1233623-1517-CM25</t>
+          <t>4291-542-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6961.5</v>
+        <v>3130.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233623-1516-CM25</t>
+          <t>4468-93-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7854</v>
+        <v>3777.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1233623-1515-CM25</t>
+          <t>2385-355-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>73468.42</v>
+        <v>31166.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1233623-1394-CM25</t>
+          <t>4291-672-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1176.91</v>
+        <v>24675.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233623-1519-CM25</t>
+          <t>3917-148-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>49245.13</v>
+        <v>26030.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1261592-8545-CM25</t>
+          <t>3916-271-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,28 +1484,28 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>70477.87</v>
+        <v>7015.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2429-3146-CM25</t>
+          <t>3053-20-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,28 +1545,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>32349.2</v>
+        <v>21123.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4291-3056-CM25</t>
+          <t>3053-21-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,43 +1606,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5660.38</v>
+        <v>19246.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3858-18-CM26</t>
+          <t>881-200-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2087.24</v>
+        <v>15628.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2385-40-CM26</t>
+          <t>881-201-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4914.64</v>
+        <v>2873.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922070-9-CM26</t>
+          <t>3917-188-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1701</v>
+        <v>30178.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2385-81-CM26</t>
+          <t>3917-189-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,43 +1850,43 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1944.91</v>
+        <v>14732.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2429-167-CM26</t>
+          <t>3917-213-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,43 +1911,43 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3094.83</v>
+        <v>27274.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>707415-28-CM26</t>
+          <t>1230848-159-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,28 +1972,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>259.42</v>
+        <v>36125.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2429-228-CM26</t>
+          <t>3858-284-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,28 +2033,28 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2057.27</v>
+        <v>17017</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3858-106-CM26</t>
+          <t>3858-297-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,43 +2094,43 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5357.86</v>
+        <v>24273.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3858-108-CM26</t>
+          <t>1233623-312-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,43 +2155,43 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2717.96</v>
+        <v>7378.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2385-172-CM26</t>
+          <t>3858-315-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,43 +2216,43 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>955.5700000000001</v>
+        <v>33893.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4291-223-CM26</t>
+          <t>1233623-301-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,28 +2277,28 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2292</v>
+        <v>5121.76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2258-2320-CM26</t>
+          <t>1233623-290-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,43 +2338,43 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15987.89</v>
+        <v>4292.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1113265-24-CM26</t>
+          <t>3858-318-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,43 +2399,43 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>52549.81</v>
+        <v>8513.799999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1113265-26-CM26</t>
+          <t>3858-322-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,43 +2460,43 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>17905.34</v>
+        <v>7468.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>558869-51-CM26</t>
+          <t>1233623-376-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,43 +2521,43 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>8473.32</v>
+        <v>35756.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2429-348-CM26</t>
+          <t>1233623-379-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,28 +2582,28 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>36042.24</v>
+        <v>10726.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1233623-123-CM26</t>
+          <t>1233623-339-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,28 +2643,28 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2777.46</v>
+        <v>4914.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2605-22-CM26</t>
+          <t>1233623-310-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2678.68</v>
+        <v>6267.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1233623-159-CM26</t>
+          <t>1233623-307-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,28 +2765,28 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8206.24</v>
+        <v>8032.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1261592-372-CM26</t>
+          <t>1233623-306-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,43 +2826,43 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>30769.12</v>
+        <v>11523.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3858-205-CM26</t>
+          <t>1233623-308-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,28 +2887,28 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>671.16</v>
+        <v>18468.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2385-272-CM26</t>
+          <t>4291-1649-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,43 +2948,43 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>17133.29</v>
+        <v>15066.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3858-208-CM26</t>
+          <t>3916-411-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,33 +3009,33 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11375.86</v>
+        <v>5942.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2605-30-CM26</t>
+          <t>2429-2507-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,43 +3070,43 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>746.2</v>
+        <v>27569.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2385-317-CM26</t>
+          <t>1233623-499-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,43 +3131,43 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6939.65</v>
+        <v>7139.86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3053-12-CM26</t>
+          <t>3858-396-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,33 +3192,33 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>25919.39</v>
+        <v>8091.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2429-573-CM26</t>
+          <t>2429-2579-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,28 +3253,28 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>30023.35</v>
+        <v>7754.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4291-624-CM26</t>
+          <t>2429-2586-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,43 +3314,43 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1517.25</v>
+        <v>6030.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3917-113-CM26</t>
+          <t>2429-2610-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,43 +3375,43 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10055.74</v>
+        <v>2584.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3917-115-CM26</t>
+          <t>4291-1992-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.427.199-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,43 +3436,43 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7150.39</v>
+        <v>3474.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1220203-67-CM26</t>
+          <t>4291-1964-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,28 +3497,28 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>21793.56</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4291-699-CM26</t>
+          <t>4291-2009-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.427.199-8</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,28 +3558,28 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>12026.22</v>
+        <v>2606.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1233822-41-CM26</t>
+          <t>1233822-60-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,43 +3619,43 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>17725.86</v>
+        <v>5534.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1233822-39-CM26</t>
+          <t>2429-2675-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,28 +3680,28 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>26022.92</v>
+        <v>3398.16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3053-19-CM26</t>
+          <t>1233623-813-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,43 +3741,43 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6814.49</v>
+        <v>56721.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1230848-128-CM26</t>
+          <t>1233623-815-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,43 +3802,43 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>12732.27</v>
+        <v>58461.65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1220203-68-CM26</t>
+          <t>4291-2240-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,28 +3863,28 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3816.45</v>
+        <v>19634.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4291-742-CM26</t>
+          <t>3845-65-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,43 +3924,43 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>904.4</v>
+        <v>9518.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4291-756-CM26</t>
+          <t>1261592-4301-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,28 +3985,28 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2345.42</v>
+        <v>5090.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2385-469-CM26</t>
+          <t>1261592-4302-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,43 +4046,43 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2885.27</v>
+        <v>25454.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4291-856-CM26</t>
+          <t>1233623-897-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,28 +4107,28 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>15346.24</v>
+        <v>63308</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1261592-723-CM26</t>
+          <t>2385-1022-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,43 +4168,43 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3811.76</v>
+        <v>15201.54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1261592-724-CM26</t>
+          <t>2429-2875-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,33 +4229,33 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11435.28</v>
+        <v>24981.79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1261592-722-CM26</t>
+          <t>558869-293-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,28 +4290,28 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>15247.04</v>
+        <v>60037.05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1261592-673-CM26</t>
+          <t>2385-1103-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,28 +4351,28 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>16292.53</v>
+        <v>10176.74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1261592-720-CM26</t>
+          <t>1233623-1319-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8894.110000000001</v>
+        <v>6294.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2605-55-CM26</t>
+          <t>2385-1120-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2240.94</v>
+        <v>1657.43</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1261592-721-CM26</t>
+          <t>1233623-1394-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>12705.87</v>
+        <v>1176.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1230848-135-CM26</t>
+          <t>1233623-1515-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,27 +4550,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2712.01</v>
+        <v>73468.42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1261592-769-CM26</t>
+          <t>1233623-1516-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,27 +4611,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2541.17</v>
+        <v>7854</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2384-118-CM26</t>
+          <t>1233623-1517-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>23243.56</v>
+        <v>6961.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2384-119-CM26</t>
+          <t>1233623-1519-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,27 +4733,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4871.55</v>
+        <v>49245.13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2384-120-CM26</t>
+          <t>1233623-1520-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3101.41</v>
+        <v>434.83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>664-36-CM26</t>
+          <t>1261592-8545-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2784.36</v>
+        <v>70477.87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3845-42-CM26</t>
+          <t>2429-3146-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>27096.3</v>
+        <v>32349.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1498185-191-CM26</t>
+          <t>4291-3056-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>65.483.190-4</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>FUND CENTRO CULTURAL PALACIO DE LA MONEDA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4517.24</v>
+        <v>5660.38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922070-185-CM26</t>
+          <t>3858-18-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3393.88</v>
+        <v>2087.24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2385-528-CM26</t>
+          <t>2385-40-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7640.64</v>
+        <v>4914.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922070-186-CM26</t>
+          <t>922070-9-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,17 +5160,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>848.47</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1158-99-CM26</t>
+          <t>2385-81-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,27 +5221,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2547.98</v>
+        <v>1944.91</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3858-332-CM26</t>
+          <t>2429-167-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1432.83</v>
+        <v>3094.83</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3834-243-CM26</t>
+          <t>707415-28-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.095.533-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1057.51</v>
+        <v>259.42</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1261592-925-CM26</t>
+          <t>2429-228-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,7 +5449,3854 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
+        <v>2057.27</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3858-106-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>5357.86</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3858-108-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>2717.96</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2385-172-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>955.5700000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4291-223-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>77.137.827-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2258-2320-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>15987.89</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1113265-24-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>62.000.770-6</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ESPEX INGENIERIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>52549.81</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1113265-26-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>62.000.770-6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>17905.34</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>558869-51-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>8473.32</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2429-348-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>36042.24</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1233623-123-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>2777.46</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2605-22-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>2678.68</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1233623-159-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>8206.24</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1261592-372-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>30769.12</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3858-205-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>671.16</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2385-272-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>17133.29</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3858-208-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>11375.86</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2605-30-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>746.2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2385-317-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>6939.65</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3053-12-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>25919.39</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2429-573-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>30023.35</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4291-624-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>1517.25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3917-113-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>10055.74</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3917-115-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>7150.39</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1220203-67-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>60.905.047-0</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>21793.56</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4291-699-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>12026.22</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1233822-41-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>65.076.481-1</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>17725.86</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1233822-39-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>65.076.481-1</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>26022.92</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3053-19-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>76.011.397-2</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>6814.49</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1230848-128-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>70.954.900-6</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.011.397-2</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>12732.27</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1220203-68-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>60.905.047-0</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>3816.45</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>4291-742-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>904.4</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>4291-756-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>2345.42</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2385-469-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>2885.27</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>4291-856-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>15346.24</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1261592-724-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>11435.28</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1261592-723-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>3811.76</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1261592-722-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>15247.04</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1261592-721-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>12705.87</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1261592-720-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>8894.110000000001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1261592-673-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>16292.53</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2605-55-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>2240.94</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1230848-135-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>70.954.900-6</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>2712.01</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1261592-769-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>2541.17</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2384-118-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>23243.56</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2384-119-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>4871.55</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2384-120-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>3101.41</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>664-36-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>61.402.017-2</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>2784.36</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>3845-42-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>27096.3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1498185-191-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>65.483.190-4</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>FUND CENTRO CULTURAL PALACIO DE LA MONEDA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>RyC Servicios Computacionales Ltda</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>4517.24</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>922070-185-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>65.117.365-5</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Antofagasta</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>3393.88</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>922070-186-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>65.117.365-5</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Antofagasta</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>848.47</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2385-528-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>7640.64</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1158-99-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>2547.98</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>3834-243-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>1057.51</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>3858-332-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>1432.83</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1261592-925-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
         <v>22355.1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>4291-1152-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>16867.36</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2384-148-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>2934.54</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1158-106-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>4823.01</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>947750-31-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>184010.89</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1233623-521-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>6218.23</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1233623-579-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>70768.14999999999</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1375735-41-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>61.981.250-6</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>4569.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>881-200-CM25</t>
+          <t>3917-189-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15628.27</v>
+        <v>14732.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>881-201-CM25</t>
+          <t>881-200-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2873.85</v>
+        <v>15628.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3917-188-CM25</t>
+          <t>881-201-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>30178.4</v>
+        <v>2873.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3917-189-CM25</t>
+          <t>3917-188-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>14732.2</v>
+        <v>30178.4</v>
       </c>
     </row>
     <row r="24">
@@ -2161,7 +2161,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3858-315-CM25</t>
+          <t>1233623-301-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>33893.4</v>
+        <v>5121.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1233623-301-CM25</t>
+          <t>3858-315-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5121.76</v>
+        <v>33893.4</v>
       </c>
     </row>
     <row r="31">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1233623-339-CM25</t>
+          <t>1233623-306-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4914.7</v>
+        <v>11523.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1233623-310-CM25</t>
+          <t>1233623-307-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6267.02</v>
+        <v>8032.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1233623-307-CM25</t>
+          <t>1233623-308-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8032.38</v>
+        <v>18468.56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1233623-306-CM25</t>
+          <t>1233623-310-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>11523.96</v>
+        <v>6267.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1233623-308-CM25</t>
+          <t>1233623-339-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>18468.56</v>
+        <v>4914.7</v>
       </c>
     </row>
     <row r="41">
@@ -2954,7 +2954,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3916-411-CM25</t>
+          <t>2429-2507-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5942.31</v>
+        <v>27569.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2429-2507-CM25</t>
+          <t>3916-411-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>27569.92</v>
+        <v>5942.31</v>
       </c>
     </row>
     <row r="44">
@@ -3686,7 +3686,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1233623-813-CM25</t>
+          <t>4291-2240-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>56721.06</v>
+        <v>19634.74</v>
       </c>
     </row>
     <row r="55">
@@ -3808,7 +3808,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4291-2240-CM25</t>
+          <t>1233623-813-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>19634.74</v>
+        <v>56721.06</v>
       </c>
     </row>
     <row r="57">
@@ -3930,7 +3930,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1261592-4301-CM25</t>
+          <t>1261592-4302-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5090.82</v>
+        <v>25454.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1261592-4302-CM25</t>
+          <t>1261592-4301-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>25454.1</v>
+        <v>5090.82</v>
       </c>
     </row>
     <row r="60">
@@ -4479,7 +4479,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1233623-1394-CM25</t>
+          <t>1233623-1520-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1176.91</v>
+        <v>434.83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1233623-1515-CM25</t>
+          <t>1233623-1519-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>73468.42</v>
+        <v>49245.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1233623-1516-CM25</t>
+          <t>1233623-1517-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>7854</v>
+        <v>6961.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1233623-1517-CM25</t>
+          <t>1233623-1516-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6961.5</v>
+        <v>7854</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1233623-1519-CM25</t>
+          <t>1233623-1515-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>49245.13</v>
+        <v>73468.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1233623-1520-CM25</t>
+          <t>1233623-1394-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>434.83</v>
+        <v>1176.91</v>
       </c>
     </row>
     <row r="73">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>707415-28-CM26</t>
+          <t>1372962-2-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.143.474-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>259.42</v>
+        <v>1462.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2429-228-CM26</t>
+          <t>1375735-7-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2057.27</v>
+        <v>51590.31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3858-106-CM26</t>
+          <t>1375735-9-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,22 +5470,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5357.86</v>
+        <v>3057.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3858-108-CM26</t>
+          <t>707415-28-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.095.533-7</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2717.96</v>
+        <v>259.42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2385-172-CM26</t>
+          <t>2429-228-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>955.5700000000001</v>
+        <v>2057.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4291-223-CM26</t>
+          <t>3858-106-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2292</v>
+        <v>5357.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2258-2320-CM26</t>
+          <t>3858-108-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,22 +5714,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>15987.89</v>
+        <v>2717.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1113265-24-CM26</t>
+          <t>2385-172-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>52549.81</v>
+        <v>955.5700000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1113265-26-CM26</t>
+          <t>4291-223-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>17905.34</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>558869-51-CM26</t>
+          <t>2258-2320-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,22 +5897,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8473.32</v>
+        <v>15987.89</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2429-348-CM26</t>
+          <t>1113265-24-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>36042.24</v>
+        <v>52549.81</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1233623-123-CM26</t>
+          <t>1113265-26-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2777.46</v>
+        <v>17905.34</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2605-22-CM26</t>
+          <t>558869-51-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,27 +6075,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2678.68</v>
+        <v>8473.32</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1233623-159-CM26</t>
+          <t>2429-348-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8206.24</v>
+        <v>36042.24</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1261592-372-CM26</t>
+          <t>1233623-123-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>30769.12</v>
+        <v>2777.46</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3858-205-CM26</t>
+          <t>2605-22-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>671.16</v>
+        <v>2678.68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2385-272-CM26</t>
+          <t>1233623-159-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,22 +6324,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>17133.29</v>
+        <v>8206.24</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3858-208-CM26</t>
+          <t>1261592-372-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,22 +6385,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>11375.86</v>
+        <v>30769.12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2605-30-CM26</t>
+          <t>3858-205-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,27 +6441,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>746.2</v>
+        <v>671.16</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2385-317-CM26</t>
+          <t>3858-208-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6939.65</v>
+        <v>11375.86</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3053-12-CM26</t>
+          <t>2385-272-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,27 +6563,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>25919.39</v>
+        <v>17133.29</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2429-573-CM26</t>
+          <t>2605-30-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>30023.35</v>
+        <v>746.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4291-624-CM26</t>
+          <t>2385-317-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1517.25</v>
+        <v>6939.65</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3917-113-CM26</t>
+          <t>3053-12-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>10055.74</v>
+        <v>25919.39</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3917-115-CM26</t>
+          <t>2429-573-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>7150.39</v>
+        <v>30023.35</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1220203-67-CM26</t>
+          <t>4291-624-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,22 +6873,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>21793.56</v>
+        <v>1517.25</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4291-699-CM26</t>
+          <t>3917-113-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>12026.22</v>
+        <v>10055.74</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1233822-41-CM26</t>
+          <t>3917-115-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>17725.86</v>
+        <v>7150.39</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1233822-39-CM26</t>
+          <t>1220203-67-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>26022.92</v>
+        <v>21793.56</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3053-19-CM26</t>
+          <t>1233822-39-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6814.49</v>
+        <v>26022.92</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1230848-128-CM26</t>
+          <t>1233822-41-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>TNS CHILE TECHNETSECURITY SA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.011.397-2</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>12732.27</v>
+        <v>17725.86</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1220203-68-CM26</t>
+          <t>4291-699-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3816.45</v>
+        <v>12026.22</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4291-742-CM26</t>
+          <t>3053-19-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>904.4</v>
+        <v>6814.49</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4291-756-CM26</t>
+          <t>1230848-128-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TNS CHILE TECHNETSECURITY SA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.011.397-2</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2345.42</v>
+        <v>12732.27</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2385-469-CM26</t>
+          <t>1220203-68-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2885.27</v>
+        <v>3816.45</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4291-856-CM26</t>
+          <t>4291-742-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>15346.24</v>
+        <v>904.4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1261592-724-CM26</t>
+          <t>2385-469-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11435.28</v>
+        <v>2885.27</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1261592-723-CM26</t>
+          <t>4291-756-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,22 +7605,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3811.76</v>
+        <v>2345.42</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1261592-722-CM26</t>
+          <t>4291-856-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,22 +7666,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>15247.04</v>
+        <v>15346.24</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1261592-721-CM26</t>
+          <t>2605-55-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>12705.87</v>
+        <v>2240.94</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1261592-720-CM26</t>
+          <t>1261592-673-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>8894.110000000001</v>
+        <v>16292.53</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1261592-673-CM26</t>
+          <t>1261592-720-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>16292.53</v>
+        <v>8894.110000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2605-55-CM26</t>
+          <t>1261592-721-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2240.94</v>
+        <v>12705.87</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1230848-135-CM26</t>
+          <t>1261592-722-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,27 +7966,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2712.01</v>
+        <v>15247.04</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1261592-769-CM26</t>
+          <t>1261592-723-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,17 +8027,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2541.17</v>
+        <v>3811.76</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2384-118-CM26</t>
+          <t>1261592-724-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8088,27 +8088,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>23243.56</v>
+        <v>11435.28</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2384-119-CM26</t>
+          <t>1261592-769-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4871.55</v>
+        <v>2541.17</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2384-120-CM26</t>
+          <t>1230848-135-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3101.41</v>
+        <v>2712.01</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>664-36-CM26</t>
+          <t>2384-118-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,22 +8276,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2784.36</v>
+        <v>23243.56</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3845-42-CM26</t>
+          <t>2384-119-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>27096.3</v>
+        <v>4871.55</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1498185-191-CM26</t>
+          <t>2384-120-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>65.483.190-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FUND CENTRO CULTURAL PALACIO DE LA MONEDA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4517.24</v>
+        <v>3101.41</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>922070-185-CM26</t>
+          <t>664-36-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,22 +8459,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3393.88</v>
+        <v>2784.36</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>922070-186-CM26</t>
+          <t>3845-42-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>848.47</v>
+        <v>27096.3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2385-528-CM26</t>
+          <t>922070-185-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>7640.64</v>
+        <v>3393.88</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1158-99-CM26</t>
+          <t>922070-186-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2547.98</v>
+        <v>848.47</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3834-243-CM26</t>
+          <t>2385-528-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1057.51</v>
+        <v>7640.64</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3858-332-CM26</t>
+          <t>1158-99-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1432.83</v>
+        <v>2547.98</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1261592-925-CM26</t>
+          <t>3834-243-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>22355.1</v>
+        <v>1057.51</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4291-1152-CM26</t>
+          <t>3858-332-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>16867.36</v>
+        <v>1432.83</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2384-148-CM26</t>
+          <t>1261592-925-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2934.54</v>
+        <v>22355.1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1158-106-CM26</t>
+          <t>4291-1152-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4823.01</v>
+        <v>16867.36</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>947750-31-CM26</t>
+          <t>2384-148-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,32 +9094,28 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>184010.89</v>
+        <v>2934.54</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1233623-521-CM26</t>
+          <t>1158-106-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9144,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9159,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9174,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>6218.23</v>
+        <v>4823.01</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1233623-579-CM26</t>
+          <t>947750-31-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9195,7 +9191,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9205,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9220,28 +9216,32 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>70768.14999999999</v>
+        <v>184010.89</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1375735-41-CM26</t>
+          <t>1233623-521-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9256,22 +9256,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9296,7 +9296,678 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
+        <v>6218.23</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1233623-579-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>70768.14999999999</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1375735-41-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>61.981.250-6</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
         <v>4569.6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1233623-685-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>60567.91</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1233623-682-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>12217.43</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1782-24-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>6197.4</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1233623-726-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>46625.34</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1994-97-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>60.511.021-5</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1997-53-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>60.511.023-1</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1604-105-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>60.511.020-7</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1220203-109-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>60.905.047-0</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>3546.2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1551737-8-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>65.281.096-9</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN DE DESAROLLO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>COBROTECH SPA</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>76.819.088-7</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>6348.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
@@ -562,7 +562,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2565,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2630,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2695,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2760,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3008,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3073,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3138,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3390,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3455,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3520,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3646,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3772,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3837,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4085,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4150,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4215,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4280,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4345,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4410,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4475,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4662,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4727,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4792,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4857,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4922,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4987,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5052,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5117,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5243,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5308,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5373,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5438,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5503,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5629,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5694,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5759,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5885,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5950,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6015,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6080,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6145,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6210,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6336,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6401,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6466,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6592,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6657,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6722,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6787,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6852,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6917,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6982,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7291,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7356,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7421,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7852,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7917,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7982,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8047,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8112,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8238,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8303,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8368,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8433,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8498,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8563,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8628,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8693,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8758,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8823,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8888,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8953,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9140,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9205,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9270,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9335,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9522,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9587,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9717,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9782,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9908,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10034,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10099,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10164,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10229,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10294,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10359,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10424,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3149-78-CM25</t>
+          <t>3834-48-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,28 +684,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26700.03</v>
+        <v>5625.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3834-48-CM25</t>
+          <t>3149-78-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -725,17 +729,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -745,26 +749,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5625.61</v>
+        <v>26700.03</v>
       </c>
     </row>
     <row r="6">
@@ -1737,7 +1737,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>881-200-CM25</t>
+          <t>3917-188-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15628.27</v>
+        <v>30178.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>881-201-CM25</t>
+          <t>881-200-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1842,17 +1842,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2873.85</v>
+        <v>15628.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3917-188-CM25</t>
+          <t>881-201-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>30178.4</v>
+        <v>2873.85</v>
       </c>
     </row>
     <row r="24">
@@ -2257,7 +2257,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1233623-301-CM25</t>
+          <t>1233623-290-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5121.76</v>
+        <v>4292.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3858-315-CM25</t>
+          <t>1233623-301-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>33893.4</v>
+        <v>5121.76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1233623-290-CM25</t>
+          <t>3858-315-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4292.33</v>
+        <v>33893.4</v>
       </c>
     </row>
     <row r="32">
@@ -2712,7 +2712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1233623-306-CM25</t>
+          <t>1233623-339-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>11523.96</v>
+        <v>4914.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1233623-307-CM25</t>
+          <t>1233623-308-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2832,13 +2832,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8032.38</v>
+        <v>18468.56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1233623-308-CM25</t>
+          <t>1233623-307-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>18468.56</v>
+        <v>8032.38</v>
       </c>
     </row>
     <row r="39">
@@ -2960,7 +2960,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1233623-339-CM25</t>
+          <t>1233623-306-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4914.7</v>
+        <v>11523.96</v>
       </c>
     </row>
     <row r="41">
@@ -3090,7 +3090,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2429-2507-CM25</t>
+          <t>3916-411-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3110,17 +3110,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3130,32 +3130,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>27569.92</v>
+        <v>5942.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3916-411-CM25</t>
+          <t>2429-2507-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3175,17 +3171,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3195,22 +3191,26 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5942.31</v>
+        <v>27569.92</v>
       </c>
     </row>
     <row r="44">
@@ -3537,7 +3537,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4291-1992-CM25</t>
+          <t>4291-1964-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3577,28 +3577,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3474.8</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4291-1964-CM25</t>
+          <t>4291-1992-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3638,26 +3642,22 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.427.199-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3451</v>
+        <v>3474.8</v>
       </c>
     </row>
     <row r="51">
@@ -3854,7 +3854,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4291-2240-CM25</t>
+          <t>1233623-813-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3874,17 +3874,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>19634.74</v>
+        <v>56721.06</v>
       </c>
     </row>
     <row r="55">
@@ -3976,7 +3976,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1233623-813-CM25</t>
+          <t>4291-2240-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3996,17 +3996,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>56721.06</v>
+        <v>19634.74</v>
       </c>
     </row>
     <row r="57">
@@ -4102,7 +4102,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1261592-4302-CM25</t>
+          <t>1261592-4301-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4161,13 +4161,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>25454.1</v>
+        <v>5090.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1261592-4301-CM25</t>
+          <t>1261592-4302-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5090.82</v>
+        <v>25454.1</v>
       </c>
     </row>
     <row r="60">
@@ -4679,7 +4679,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1233623-1520-CM25</t>
+          <t>1233623-1394-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>434.83</v>
+        <v>1176.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1233623-1519-CM25</t>
+          <t>1233623-1515-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4803,13 +4803,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>49245.13</v>
+        <v>73468.42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1233623-1517-CM25</t>
+          <t>1233623-1516-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4868,13 +4868,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>6961.5</v>
+        <v>7854</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1233623-1516-CM25</t>
+          <t>1233623-1517-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7854</v>
+        <v>6961.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1233623-1515-CM25</t>
+          <t>1233623-1519-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>73468.42</v>
+        <v>49245.13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1233623-1394-CM25</t>
+          <t>1233623-1520-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1176.91</v>
+        <v>434.83</v>
       </c>
     </row>
     <row r="73">
@@ -5581,7 +5581,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1372962-2-CM26</t>
+          <t>1375735-9-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5601,17 +5601,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>65.143.474-2</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1462.27</v>
+        <v>3057.23</v>
       </c>
     </row>
     <row r="82">
@@ -5711,7 +5711,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1375735-9-CM26</t>
+          <t>1372962-2-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>65.143.474-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3057.23</v>
+        <v>1462.27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>707415-28-CM26</t>
+          <t>2429-228-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5816,28 +5816,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>259.42</v>
+        <v>2057.27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2429-228-CM26</t>
+          <t>707415-28-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5862,12 +5866,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5877,32 +5881,28 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.095.533-7</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2057.27</v>
+        <v>259.42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3858-106-CM26</t>
+          <t>3858-108-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5961,13 +5961,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5357.86</v>
+        <v>2717.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3858-108-CM26</t>
+          <t>3858-106-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2717.96</v>
+        <v>5357.86</v>
       </c>
     </row>
     <row r="88">
@@ -6544,7 +6544,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2605-22-CM26</t>
+          <t>1233623-159-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2678.68</v>
+        <v>8206.24</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1233623-159-CM26</t>
+          <t>2605-22-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>8206.24</v>
+        <v>2678.68</v>
       </c>
     </row>
     <row r="98">
@@ -6804,7 +6804,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3858-208-CM26</t>
+          <t>2385-272-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6863,13 +6863,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>11375.86</v>
+        <v>17133.29</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2385-272-CM26</t>
+          <t>3858-208-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>17133.29</v>
+        <v>11375.86</v>
       </c>
     </row>
     <row r="102">
@@ -7499,7 +7499,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1233822-41-CM26</t>
+          <t>4291-699-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7519,17 +7519,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7554,13 +7554,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>17725.86</v>
+        <v>12026.22</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4291-699-CM26</t>
+          <t>1233822-41-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7580,17 +7580,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>12026.22</v>
+        <v>17725.86</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3053-19-CM26</t>
+          <t>1230848-128-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7641,17 +7641,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7676,13 +7676,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6814.49</v>
+        <v>12732.27</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1230848-128-CM26</t>
+          <t>3053-19-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7702,17 +7702,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>12732.27</v>
+        <v>6814.49</v>
       </c>
     </row>
     <row r="115">
@@ -8255,7 +8255,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1261592-721-CM26</t>
+          <t>1261592-722-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8314,13 +8314,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>12705.87</v>
+        <v>15247.04</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1261592-722-CM26</t>
+          <t>1261592-721-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8379,7 +8379,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>15247.04</v>
+        <v>12705.87</v>
       </c>
     </row>
     <row r="125">
@@ -8515,7 +8515,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1261592-769-CM26</t>
+          <t>1230848-135-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8535,17 +8535,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8574,13 +8574,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2541.17</v>
+        <v>2712.01</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1230848-135-CM26</t>
+          <t>1261592-769-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8600,17 +8600,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8620,12 +8620,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2712.01</v>
+        <v>2541.17</v>
       </c>
     </row>
     <row r="129">
@@ -9222,7 +9222,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3834-243-CM26</t>
+          <t>3858-332-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9281,13 +9281,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1057.51</v>
+        <v>1432.83</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3858-332-CM26</t>
+          <t>3834-243-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1432.83</v>
+        <v>1057.51</v>
       </c>
     </row>
     <row r="140">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10436,6 +10436,957 @@
       </c>
       <c r="M156" s="2" t="n">
         <v>6348.65</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2385-765-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>1965.4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1233623-942-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>31600.45</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>3858-451-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>2017.05</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1233623-973-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>46731.3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2429-1297-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>11369.24</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>558869-261-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>67004.14</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>558869-260-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>68889.53</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>558869-259-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>72653.07000000001</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>558869-263-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>66346.95</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>558869-262-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>72943.38</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1103675-2-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>3957.42</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1103675-1-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>62626.84</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2429-1309-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>30273.22</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2429-1304-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>33653.5</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>558869-279-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>71702.56</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
@@ -9372,7 +9372,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1737,7 +1737,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3917-188-CM25</t>
+          <t>881-201-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>30178.4</v>
+        <v>2873.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>881-200-CM25</t>
+          <t>3917-188-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>15628.27</v>
+        <v>30178.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>881-201-CM25</t>
+          <t>881-200-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2873.85</v>
+        <v>15628.27</v>
       </c>
     </row>
     <row r="24">
@@ -2777,7 +2777,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1233623-308-CM25</t>
+          <t>1233623-307-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2832,13 +2832,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>18468.56</v>
+        <v>8032.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1233623-307-CM25</t>
+          <t>1233623-308-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8032.38</v>
+        <v>18468.56</v>
       </c>
     </row>
     <row r="39">
@@ -4679,7 +4679,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1233623-1394-CM25</t>
+          <t>1233623-1517-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1176.91</v>
+        <v>6961.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1233623-1515-CM25</t>
+          <t>1233623-1394-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4784,17 +4784,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4803,13 +4803,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>73468.42</v>
+        <v>1176.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1233623-1516-CM25</t>
+          <t>1233623-1515-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4849,17 +4849,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4868,13 +4868,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>7854</v>
+        <v>73468.42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1233623-1517-CM25</t>
+          <t>1233623-1520-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6961.5</v>
+        <v>434.83</v>
       </c>
     </row>
     <row r="71">
@@ -5004,7 +5004,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1233623-1520-CM25</t>
+          <t>1233623-1516-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>434.83</v>
+        <v>7854</v>
       </c>
     </row>
     <row r="73">
@@ -5581,7 +5581,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1375735-9-CM26</t>
+          <t>1375735-7-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3057.23</v>
+        <v>51590.31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1375735-7-CM26</t>
+          <t>1372962-2-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>65.143.474-2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5705,13 +5705,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>51590.31</v>
+        <v>1462.27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1372962-2-CM26</t>
+          <t>1375735-9-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>65.143.474-2</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>FUNDACION PARA LA REHABILITACIÓN DE PERSONAS CON DISCAPACIDAD DE LA COMUNA DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1462.27</v>
+        <v>3057.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2429-228-CM26</t>
+          <t>707415-28-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5816,32 +5816,28 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.095.533-7</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2057.27</v>
+        <v>259.42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>707415-28-CM26</t>
+          <t>2429-228-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5866,12 +5862,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5881,28 +5877,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Ingenieria y Tecnologia Kropsys Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.095.533-7</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>259.42</v>
+        <v>2057.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3858-108-CM26</t>
+          <t>3858-106-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5961,13 +5961,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2717.96</v>
+        <v>5357.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3858-106-CM26</t>
+          <t>3858-108-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5357.86</v>
+        <v>2717.96</v>
       </c>
     </row>
     <row r="88">
@@ -6544,7 +6544,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1233623-159-CM26</t>
+          <t>2605-22-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8206.24</v>
+        <v>2678.68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2605-22-CM26</t>
+          <t>1233623-159-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2678.68</v>
+        <v>8206.24</v>
       </c>
     </row>
     <row r="98">
@@ -7438,7 +7438,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1233822-39-CM26</t>
+          <t>4291-699-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7458,17 +7458,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7493,13 +7493,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>26022.92</v>
+        <v>12026.22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4291-699-CM26</t>
+          <t>1233822-39-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7519,17 +7519,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>12026.22</v>
+        <v>26022.92</v>
       </c>
     </row>
     <row r="112">
@@ -7621,7 +7621,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1230848-128-CM26</t>
+          <t>3053-19-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7641,17 +7641,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7676,13 +7676,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>12732.27</v>
+        <v>6814.49</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3053-19-CM26</t>
+          <t>1230848-128-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7702,17 +7702,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6814.49</v>
+        <v>12732.27</v>
       </c>
     </row>
     <row r="115">
@@ -7869,7 +7869,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2385-469-CM26</t>
+          <t>4291-756-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7928,13 +7928,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2885.27</v>
+        <v>2345.42</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4291-756-CM26</t>
+          <t>2385-469-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7954,17 +7954,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2345.42</v>
+        <v>2885.27</v>
       </c>
     </row>
     <row r="119">
@@ -8064,7 +8064,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2605-55-CM26</t>
+          <t>1261592-722-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8123,13 +8123,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2240.94</v>
+        <v>15247.04</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1261592-673-CM26</t>
+          <t>1261592-720-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8169,28 +8169,32 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>16292.53</v>
+        <v>8894.110000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1261592-720-CM26</t>
+          <t>1261592-673-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8230,32 +8234,28 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8894.110000000001</v>
+        <v>16292.53</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1261592-722-CM26</t>
+          <t>1261592-724-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8314,13 +8314,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>15247.04</v>
+        <v>11435.28</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1261592-721-CM26</t>
+          <t>2605-55-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8379,13 +8379,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>12705.87</v>
+        <v>2240.94</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1261592-723-CM26</t>
+          <t>1261592-721-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3811.76</v>
+        <v>12705.87</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1261592-724-CM26</t>
+          <t>1261592-723-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>11435.28</v>
+        <v>3811.76</v>
       </c>
     </row>
     <row r="127">
@@ -9222,7 +9222,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3858-332-CM26</t>
+          <t>3834-243-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9281,13 +9281,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1432.83</v>
+        <v>1057.51</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3834-243-CM26</t>
+          <t>3858-332-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1057.51</v>
+        <v>1432.83</v>
       </c>
     </row>
     <row r="140">
@@ -10754,7 +10754,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>558869-261-CM26</t>
+          <t>558869-260-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10794,28 +10794,32 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>67004.14</v>
+        <v>68889.53</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>558869-260-CM26</t>
+          <t>558869-259-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10855,12 +10859,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10874,13 +10878,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>68889.53</v>
+        <v>72653.07000000001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>558869-259-CM26</t>
+          <t>558869-261-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10920,32 +10924,28 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>72653.07000000001</v>
+        <v>67004.14</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>558869-263-CM26</t>
+          <t>1230848-223-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10985,28 +10985,32 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>66346.95</v>
+        <v>3091.16</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>558869-262-CM26</t>
+          <t>1230848-220-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11031,12 +11035,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11046,32 +11050,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>72943.38</v>
+        <v>25074.74</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1103675-2-CM26</t>
+          <t>1103675-1-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11111,28 +11111,32 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3957.42</v>
+        <v>62626.84</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1103675-1-CM26</t>
+          <t>1103675-2-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11172,32 +11176,28 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>62626.84</v>
+        <v>3957.42</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2429-1309-CM26</t>
+          <t>558869-262-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11222,12 +11222,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11256,13 +11256,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>30273.22</v>
+        <v>72943.38</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2429-1304-CM26</t>
+          <t>558869-263-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11302,91 +11302,217 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>33653.5</v>
+        <v>66346.95</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
+          <t>2429-1304-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>33653.5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t>558869-279-CM26</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>2239-5-LR25</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>71.102.600-2</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
         <is>
           <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="J172" t="inlineStr">
         <is>
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="K172" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="n">
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
         <v>71702.56</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2429-1309-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>30273.22</v>
       </c>
     </row>
   </sheetData>
